--- a/custom-roles-test-cases.xlsx
+++ b/custom-roles-test-cases.xlsx
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Verification status: VIU (Verify-in-UI) has BEGUN (pass 1, staging, 2026-07-01). 15 findings logged (10 MATCH / 5 DISCREPANCY) — see the 'VIU Findings Log' tab. 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
+          <t>Verification status: VIU (Verify-in-UI) has BEGUN (pass 1, staging, 2026-07-01). 15 findings logged (11 MATCH / 4 DISCREPANCY (VIU-05 corrected to MATCH 2026-07-01)) — see the 'VIU Findings Log' tab. 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -796,22 +796,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Edit = inline pencil icon; kebab menu has ONLY 'View Permissions'; NO Delete action for any role (system or custom)</t>
+          <t>Custom roles: kebab (three-dot) menu contains 'View Permissions' + 'Delete'. System roles: kebab has 'View Permissions' only (no Delete). Locked roles (Office, Time Clock): view-only (eye icon). Edit is an inline pencil icon on editable roles.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY (Delete absent; Edit is an icon not a menu item)</t>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>actions-menu-system.png, actions-menu-custom.png</t>
+          <t>02-roles-list.png; user screenshot 2026-07-01</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Entire SV-7502 Delete-Role flow appears unimplemented in the UI.</t>
+          <t>Corrected 2026-07-01 per user screenshot — earlier probe had only inspected a System role's kebab and wrongly concluded Delete was absent. Delete IS available for Custom roles, matching spec (SV-7502).</t>
         </is>
       </c>
     </row>

--- a/custom-roles-test-cases.xlsx
+++ b/custom-roles-test-cases.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Digital Inspections" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VIU Findings Log'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VIU Findings Log'!$A$1:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Single Permission'!$A$1:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Template Edit'!$A$1:$H$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Combination - Representative'!$A$1:$H$11</definedName>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Verification status: VIU (Verify-in-UI) has BEGUN (pass 1, staging, 2026-07-01). 15 findings logged (11 MATCH / 4 DISCREPANCY (VIU-05 corrected to MATCH 2026-07-01)) — see the 'VIU Findings Log' tab. 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
+          <t>Verification status: VIU (Verify-in-UI) pass 2 complete (staging, live admin session, 2026-07-01). 25 findings logged (17 MATCH / 8 DISCREPANCY) — see the 'VIU Findings Log' tab. Pass 2 confirmed exact Custom Roles labels, the silent CRUD cascade, the 'Enable See Financial Data?' popup, and the kebab-menu variants, and logged 3 build-vs-spec discrepancies (doubled '/api/api/sso/check' path, no unsaved-changes guard on Create Role X-close, and the silent-cascade vs confirmation-popup dependency-UX inconsistency). 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1153,8 +1153,378 @@
       </c>
       <c r="G16" s="3" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>VIU-16</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Create-role entry point &amp; template picker</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Template selection → Role details → Permission editor → Save</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Button labelled exactly 'Create Custom Role' opens a template picker titled 'Choose a template' (subtext 'Start from a template to pre-fill settings, or skip to start from scratch') listing 11 system templates with 'Skip' and 'Apply' buttons. After Skip/Apply → 'Create Role' form with two sections: 'Basic Details' (Role Name [required], Description) and 'Permissions'.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH (exact labels confirmed)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Confirms/extends VIU-04 and VIU-08 with the exact picker title, subtext, 11-template count, and Skip/Apply button labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>VIU-17</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Permission-tree section headings &amp; controls</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Areas: Work Orders, WO Lines, Schedule, Customers, Invoicing, Timesheets, Page Access, cross-cutting toggles</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Exact headings: 'Work orders' (View / Create &amp; Edit / Delete; 'View mode' segmented control Full View / Tech view; toggles 'Review work orders', 'Pick parts', 'Order parts'); 'Work order lines' (Create &amp; Edit / Delete — NO View); 'Schedule' (View / Create &amp; Edit / Delete); 'Customers' (View / Create &amp; Edit / Delete); 'Invoicing &amp; payments' (View / Create &amp; Edit / 'Delete / Reverse'); 'Timesheets' (View / Create &amp; Edit — NO Delete); 'Page Access' toggles: 'Parts Department', 'Reports', 'Customer portal', 'Settings', 'Billing Portal'; 'Cross-Cutting Toggles': 'See Financial Data', 'View and Manage AP/AR Data', 'View History Logs'. Permission search box present; footer buttons 'Cancel' / 'Create'.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH (exact section labels captured)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>The edit tier is labelled 'Create &amp; Edit' (not 'Edit'); WO Lines has no independent View; Timesheets has no Delete; there is a permission search box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>VIU-18</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Invoicing third control label ('Delete / Reverse')</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing &amp; Payments: View / Edit / Delete</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>The Invoicing &amp; payments third (delete-tier) control is labelled exactly 'Delete / Reverse', not just 'Delete'. Other CRUD sections use plain 'Delete'.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — DISCREPANCY (label 'Delete / Reverse')</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Test cases that reference 'Invoicing Delete' should read the control as 'Delete / Reverse' in the editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>VIU-19</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>View mode control (Full View / Tech view)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Tech vs Full; UX only, not access control</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Segmented 'View mode' control under Work orders with options 'Full View' and 'Tech view'.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Confirms VIU-14 (option labels 'Full View' / 'Tech view').</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>VIU-20</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>CRUD tier cascade is SILENT (no popup)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CRUD cascade both directions</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Intra-section CRUD tiers cascade silently with no confirmation popup: enabling 'Create &amp; Edit' auto-enables 'View'; enabling 'Delete' auto-enables View + Create &amp; Edit; turning 'View' OFF force-disables Create &amp; Edit + Delete (View is master). Confirmed on Customers: Delete with all off auto-enables View + Create &amp; Edit + Delete silently.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Confirms VIU-09/VIU-10; adds that the cascade is silent (no modal) and that View acts as master for its section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>VIU-21</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Invoicing → See Financial Data confirmation popup (exact text)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Trigger on enabling Invoicing CRUD while See Financial Data OFF</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Enabling Invoicing 'Create &amp; Edit' or 'Delete / Reverse' while 'See Financial Data' is OFF shows a confirmation popup — title 'Enable See Financial Data?', body 'Invoicing &amp; Payments requires See Financial Data. Enable it to grant this permission?', buttons [Cancel] [Enable]. Enable auto-enables Invoicing View+Create&amp;Edit AND See Financial Data. Cancel changes nothing (permission blocked until dependency accepted).</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH (exact popup text captured)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Confirms VIU-11 with exact title/body/button text. Cross-Cutting toggles (See Financial Data / View and Manage AP/AR Data / View History Logs) toggle independently — no popup, no mutual auto-enable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>VIU-22</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kebab (⋮) menu variants</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Row actions: Edit / Delete / View Permissions</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Custom role with 0 users (deletable): kebab has 'View Permissions' and 'Delete' (Delete shown in red). Custom role WITH users (not deletable): kebab has only 'View Permissions' (Delete hidden). System roles: kebab has only 'View Permissions'. Locked system roles (Time Clock, Office): NO kebab at all — view-only eye icon + lock icon.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live admin session, 2026-07-01) — MATCH</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Confirms/supersedes VIU-05: Delete IS available for deletable Custom roles, but is hidden for Custom roles that have users assigned. Also confirms VIU-06 (locked roles have no kebab).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>VIU-23</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Doubled '/api' prefix on SSO auth-check (session hydration bug)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Valid cookie session should hydrate the SPA without bouncing an authenticated user to /login</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Staging auto-auth-check requests '/api/api/sso/check' (doubled '/api' prefix, because the axios baseURL already includes /api) → 404, so a valid cookie session does NOT hydrate the SPA and authenticated users are bounced to /login. Correct path should be '/api/sso/check'.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>DISCREPANCY (functional bug; severity high — blocks session hydration on staging)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Functional build bug, not a spec-wording issue. UI observation only; no secrets/session data recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>VIU-24</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>No unsaved-changes confirmation on Create Role dialog X-close</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Unsaved edits should be protected by a discard/unsaved-changes confirmation</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Closing the Create Role dialog via the X with unsaved permission toggles shows NO unsaved-changes / discard confirmation — the changes are silently dropped.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>DISCREPANCY (UX; unsaved changes silently discarded)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Contrast with the Cancel/X footer; no guard against accidental data loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>VIU-25</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Dependency-UX inconsistency (silent cascade vs confirmation popup)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Consistent UX for permission 'requires' dependencies</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Two different UX treatments for the same underlying 'requires' pattern: intra-section CRUD dependencies auto-cascade SILENTLY (see VIU-20), but the Invoicing → See Financial Data dependency uses an explicit confirmation popup (see VIU-21).</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>DISCREPANCY (UX inconsistency)</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>VIU pass 2 live admin session 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Same 'requires' relationship, two divergent UX patterns.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3559,7 +3929,7 @@
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>1. As admin, follow the admin flow to create the custom role. (Step 1 is a 'Choose a template' dialog with Skip / Apply; the footer save button on the Create Role page is labelled 'Create'.)
-2. With See Financial Data OFF, enable Invoicing &amp; Payments View (or any Invoicing CRUD).
+2. With See Financial Data OFF, enable Invoicing &amp; Payments 'Create &amp; Edit' or 'Delete / Reverse' (View alone does NOT trigger the modal).
 3. Click Confirm.
 4. Repeat and click Cancel instead.</t>
         </is>
@@ -3567,10 +3937,10 @@
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Step 1: Create Custom Role dialog opens from a blank/no-access template with all permissions OFF.
-Step 2: Financial confirm modal appears: Modal title: "Enable See Financial Data?" Body: "[Area] requires See Financial Data. Enable it to grant this permission?" Buttons: "Cancel" / "Enable" Confirm auto-enables &amp; applies; Cancel reverts. [Build-vs-spec: spec wording differed — see VIU-11.]
+Step 2: Financial confirm modal appears: Modal title: "Enable See Financial Data?" Body: "Invoicing &amp; Payments requires See Financial Data. Enable it to grant this permission?" Buttons: "Cancel" / "Enable". Enable auto-enables See Financial Data and applies Invoicing View+Create&amp;Edit; Cancel changes nothing. [Build-vs-spec: exact wording confirmed live — see VIU-11 and VIU-21.]
 Step 3: See Financial Data auto-enables and the Invoicing checkbox is applied.
 Step 4: The change reverts; See Financial Data stays OFF and the Invoicing checkbox is not applied.
-Overall: Enabling any Invoicing CRUD while See Financial Data is OFF triggers the financial confirm modal; Confirm auto-enables Financial, Cancel reverts.
+Overall: Enabling Invoicing 'Create &amp; Edit' or 'Delete / Reverse' while See Financial Data is OFF triggers the financial confirm modal ('Enable See Financial Data?'); Enable auto-enables Financial + Invoicing View+Create&amp;Edit, Cancel changes nothing. (View alone does not trigger it.)
 VIU status: Spec: Invoicing financial gate — any CRUD triggers confirm modal if See Financial Data OFF. VERIFIED (staging 2026-07-01) — DISCREPANCY; see VIU-11</t>
         </is>
       </c>
@@ -3672,7 +4042,7 @@
         <is>
           <t>1. As admin, follow the admin flow to create the custom role. (Step 1 is a 'Choose a template' dialog with Skip / Apply; the footer save button on the Create Role page is labelled 'Create'.)
 2. Enable See Financial Data; keep View and Manage AP/AR Data OFF.
-3. Enable Invoicing &amp; Payments Delete.
+3. Enable Invoicing &amp; Payments 'Delete / Reverse' (the delete-tier control in this section is labelled 'Delete / Reverse', not plain 'Delete').
 4. Confirm/enable View and Manage AP/AR Data.</t>
         </is>
       </c>
@@ -3680,7 +4050,7 @@
         <is>
           <t>Step 1: Create Custom Role dialog opens from a blank/no-access template with all permissions OFF.
 Step 2: Financial ON; View and Manage AP/AR Data OFF.
-Step 3: The AP/AR gate is enforced: Invoicing Delete additionally requires View and Manage AP/AR Data (a confirm modal / requirement is shown to enable View and Manage AP/AR Data).
+Step 3: The AP/AR gate is enforced: Invoicing Delete / Reverse additionally requires View and Manage AP/AR Data (a confirm modal / requirement is shown to enable View and Manage AP/AR Data).
 Step 4: View and Manage AP/AR Data enables and Invoicing Delete (with Edit+View cascade) is applied.
 Overall: Invoicing Delete cannot be applied without View and Manage AP/AR Data; the AP/AR gate enforces enabling View and Manage AP/AR Data (in addition to the financial gate).
 VIU status: Spec: Invoicing Delete additionally requires Manage AP/AR (AP/AR gate). UNVERIFIED — VIU pending.</t>
@@ -10862,7 +11232,7 @@
           <t>Step 1: Create Custom Role form opens with every permission toggle OFF by default. Role name accepted.
 Step 2: Parts Dept ON (children enabled). WO Edit cascades WO View ON; WO sub-settings available.
 Step 3: Each Edit cascades its View ON. No Delete enabled anywhere.
-Step 4: Both cascade View ON. Financial confirm modal(s): Modal title: "Enable See Financial Data?" Body: "Invoicing/Part Sales requires See Financial Data. Enable it to grant this permission?" Buttons: "Cancel" / "Enable" — click Enable; See Financial Data ON. [Build-vs-spec: spec wording differed — see VIU-11.]
+Step 4: Both cascade View ON. Financial confirm modal(s): Modal title: "Enable See Financial Data?" Body for Invoicing (confirmed exact): "Invoicing &amp; Payments requires See Financial Data. Enable it to grant this permission?" (the Part Sales modal substitutes its own area name). Buttons: "Cancel" / "Enable" — click Enable; See Financial Data ON. [Build-vs-spec: exact Invoicing wording confirmed live — see VIU-11 and VIU-21.]
 Step 5: Sub-settings, AP/AR, Reports ON. All Delete toggles confirmed OFF.
 Step 6: Role saved with exactly the configured toggles. Staff assignment saved. A role change forces the affected user to be logged out.
 Step 7: Login succeeds; the user sees only navigation permitted by the assigned role.

--- a/custom-roles-test-cases.xlsx
+++ b/custom-roles-test-cases.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Digital Inspections" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VIU Findings Log'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VIU Findings Log'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Single Permission'!$A$1:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Template Edit'!$A$1:$H$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Combination - Representative'!$A$1:$H$11</definedName>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Verification status: VIU (Verify-in-UI) pass 2 complete (staging, live admin session, 2026-07-01). 25 findings logged (17 MATCH / 8 DISCREPANCY) — see the 'VIU Findings Log' tab. Pass 2 confirmed exact Custom Roles labels, the silent CRUD cascade, the 'Enable See Financial Data?' popup, and the kebab-menu variants, and logged 3 build-vs-spec discrepancies (doubled '/api/api/sso/check' path, no unsaved-changes guard on Create Role X-close, and the silent-cascade vs confirmation-popup dependency-UX inconsistency). 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
+          <t>Verification status: VIU (Verify-in-UI) pass 3 complete — per-role verified as the restricted Tech user (tech@shopview.com) on staging, 2026-07-01. 31 findings logged (21 MATCH / 10 DISCREPANCY) — see the 'VIU Findings Log' tab. Pass 2 (live admin session) confirmed exact Custom Roles labels, the silent CRUD cascade, the 'Enable See Financial Data?' popup, and the kebab-menu variants. Pass 3 logged in AS Tech and verified all 11 per-role gate configs behave PER SPEC: CRUD gating (View-only read-only/no New; +Create&amp;Edit shows New; +Delete per-row delete), page-access nav gating (Reports/Customers/combination exact), Settings routes under '/administration', and view-mode/parts/financial effects carried in the permission wrapper (effects inside the WO detail / invoicing). Discrepancies/limits logged: '/settings' 404s (admin lives at '/administration'), a zero-permission role is not creatable (min 1 permission enforced), and permission changes require the user to re-login + settle. Earlier build-vs-spec discrepancies still stand (doubled '/api/api/sso/check' path, no unsaved-changes guard on Create Role X-close, silent-cascade vs confirmation-popup dependency-UX inconsistency). 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1523,8 +1523,230 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>VIU-26</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Per-role CRUD gating on the restricted Tech user (live login)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>A role granting WO View only should let the user read Work Orders but not create/edit/delete; adding Create &amp; Edit should expose New/edit; adding Delete should expose per-row delete.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Logged in AS the restricted 'Tech' user (tech@shopview.com) after assigning each config as admin and re-logging-in as Tech. WO View only: Tech sees ONLY the Work Orders nav; WO list is read-only with NO 'New' button and other modules hidden. WO View + Create &amp; Edit: the 'New' button appears (create/edit enabled), no delete. WO View + Create &amp; Edit + Delete: full WO management including per-row delete. All three behaved PER SPEC.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — MATCH</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Confirms the runtime effect of the CRUD tiers on a real restricted user, complementing the editor-side cascade findings (VIU-09/10/20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>VIU-27</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Per-role page-access nav gating (Reports / Customers / combination) on Tech</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Page-access toggles and area View permissions should gate the exact nav set the user sees.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>As Tech: Customers View only → ONLY Customers nav, read-only list, other modules hidden. Page Access Reports ON → Reports nav + report suite visible; OFF → Reports nav hidden (gate is exact). Combination WO View + Customers View + Reports ON → nav = EXACTLY Work Orders, Customers, Reports and nothing else. All behaved PER SPEC.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — MATCH</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Nav is the exact union of granted areas + enabled page-access toggles; no leakage of ungranted modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>VIU-28</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Settings/admin routes live under /administration (not /settings)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Page Access Settings ON should expose the Settings/admin routes (Settings, Staff, Roles &amp; Permissions, Locations, Departments).</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>As Tech with Page Access Settings ON: the settings routes are visible under the Administration area — they are CHILDREN of '/administration' (Settings, Staff, Roles &amp; Permissions, Locations, Departments). Navigating to '/settings' returns a 404 'coffee break' page; the working path is '/administration'.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — DISCREPANCY (path drift: spec/docs may say /settings; actual is /administration, and /settings 404s)</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>D1: correct any admin/role-config navigation that says '/settings' to '/administration'. In this suite the test-case JSON already navigates to '/administration/roles-permissions', so no literal '/settings' URL required correcting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>VIU-29</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>View-mode / parts / financial effects carried in wrapper; verified inside WO detail</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WO View Mode (Tech/Full), WO sub-toggles (Pick parts / Order parts), and See Financial Data should take effect for the assigned user.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>As Tech: the permission wrapper carries view_mode (tech / woTechViewMode), woPickParts/woOrderParts, and seeFinancialData (true/false) correctly. The visible effects manifest INSIDE the WO detail page (and invoicing for financial), NOT on the WO list: the WO list looks the same in Tech vs Full view; Pick/Order parts actions live inside the WO detail; financial figures/prices are not on the WO list and appear in WO detail / invoicing. All behaved PER SPEC.</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — MATCH (with verification-location note)</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>D3: verification steps for view-mode, delete, pick/order-parts, and see-financial-data must inspect the WO detail (invoicing for financial), not the WO list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>VIU-30</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Empty (zero-permission) role is not creatable</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>A no-access baseline role could be created with zero permissions to represent a true no-access user.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Attempting to create a role with zero permissions is rejected — the API enforces 'At least one permission is required.' A true no-access role is therefore not configurable; the minimal case is a single-permission role (e.g. timesheetsView → Tech lands on own Timesheets with an empty top nav).</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — DISCREPANCY (design limit: min 1 permission enforced)</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>D2: document as a known constraint; any 'empty role' baseline should use a single-permission minimal role instead. No such empty-role baseline login case exists in this suite, so none required conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>VIU-31</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Permission propagation requires re-login + brief settle</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>After reassigning a role to a user, the new permissions should apply to that user.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>After reassigning a role to the Tech user, the new permissions take effect only after the user logs out and logs back in (fresh login) AND a brief settle. Without a fresh login the prior permission set persists. Behaved as observed on every per-role reassignment.</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED (staging, live per-role Tech session, 2026-07-01) — behavior note</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>staging, live per-role (Tech) session, 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>D4: added as a precondition/note to per-role (assign-and-login-as-user) cases: 'After assigning the role, log out and log back in as the user (fresh login) so the new permissions load.'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10777,7 +10999,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View; Customers &gt; View; Schedule &gt; View. OFF: everything else — no WO Edit/Delete, no WO Lines, no Customers Edit/Delete, no Schedule Edit/Delete, See Financial Data OFF, Invoicing OFF, Parts Department OFF, Part Sales OFF, Catalog OFF, Vendor OFF, Reports OFF, Timesheets OFF, History Logs OFF, Settings OFF, App Settings OFF, View and Manage AP/AR Data OFF. View Mode = Full (UX only).
 Test data: Test staff user 'frontdesk_qa'. One existing work order, one customer, one schedule entry.
 Permission under test: WO View + Customers View + Schedule View, no create/edit/delete, financials OFF | Original type: Combination | Dependency mode: None</t>
@@ -10836,7 +11058,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Schedule &gt; View, Edit, Delete; Work Orders &gt; View; Customers &gt; View. OFF: everything else — WO Edit/Delete, WO Lines, Customers Edit/Delete, See Financial Data, Invoicing, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'scheduler_qa'. Existing schedule entries, work orders, customers.
 Permission under test: Schedule V/E/D + WO View + Customers View, nothing financial | Original type: Combination | Dependency mode: Cascade: auto-enable lower</t>
@@ -10897,7 +11119,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View; Work Order Lines &gt; View, Edit; WO sub-setting Pick Parts; View Mode = Tech View. OFF: everything else — WO Edit/Delete, WO Lines Delete, Review and Order sub-settings, See Financial Data, Invoicing, Parts Department, Part Sales, Catalog, Vendor, Customers, Schedule, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'jrtech_qa'. Work order with lines to pick parts on.
 Permission under test: WO View + WO Lines Edit + Pick Parts + Tech View, financials OFF | Original type: Combination | Dependency mode: Cascade: auto-enable lower</t>
@@ -10911,7 +11133,7 @@
 4. Enable WO sub-setting Pick Parts; set View Mode = Tech View. Leave Review, Order, WO Lines Delete OFF.
 5. Save the role, then go Administration &gt; Staff &gt; open the test user &gt; assign role 'Junior Tech' &gt; Create.
 6. In a separate browser, log in as the test staff user.
-7. POSITIVE: Confirm the UI presents in Tech View. Open a work order, view lines, edit a line, and pick parts.
+7. POSITIVE: Open a work order and confirm the Tech View presentation INSIDE the WO detail page (the WO list looks the same in Tech vs Full view — the difference is on the WO detail). View lines, edit a line, and use Pick Parts (Pick Parts lives inside the WO detail).
 8. NEGATIVE (aggregate): Attempt to edit the WO header, delete a line, use Review/Order actions; check nav for Invoicing/Customers/Schedule/Reports/Parts and financials.</t>
         </is>
       </c>
@@ -10923,7 +11145,7 @@
 Step 4: Pick Parts ON; View Mode = Tech (UX only). Review/Order remain OFF.
 Step 5: Role saved with exactly the configured toggles. Staff assignment saved. A role change forces the affected user to be logged out.
 Step 6: Login succeeds; the user sees only navigation permitted by the assigned role.
-Step 7: Tech View layout shown. WO viewable, lines editable, Pick Parts action available and works.
+Step 7: Tech View layout shown inside the WO detail page. WO viewable, lines editable, Pick Parts action available inside the WO detail and works. [Verification location per VIU-29: view-mode and pick/order-parts effects manifest in the WO detail, not the WO list.]
 Step 8: WO header not editable, line delete unavailable, Review/Order actions absent. Invoicing, Customers, Schedule, Reports, Parts hidden. No financial figures visible.
 Overall: Junior Tech in Tech View can view WOs, edit lines, and pick parts only. WO Lines Edit cascaded View ON. No header edit, no delete, no financials/other areas.
 VIU status: Spec: SV-7388 WO sub-settings require WO View; CRUD cascade; View Mode UX-only. VERIFIED (staging 2026-07-01) — MATCH; see VIU Findings Log</t>
@@ -10958,7 +11180,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Parts Department (parent); Catalog &gt; View, Edit; Vendor &gt; View; Part Sales &gt; View; See Financial Data. OFF: everything else — Catalog Delete, Vendor Edit/Delete, Part Sales Edit/Delete, Work Orders, WO Lines, Customers, Schedule, Invoicing, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'partsclerk_qa'. Existing catalog items, vendors, part-sale records.
 Permission under test: Parts Department ON + Catalog V/E + Vendor V + Part Sales V, See Financial Data ON, no WO/Schedule | Original type: Combination | Dependency mode: Multiple</t>
@@ -11023,7 +11245,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View; Invoicing &gt; View, Edit; See Financial Data. OFF: everything else — WO Edit/Delete, WO Lines, Invoicing Delete, View and Manage AP/AR Data, Customers, Schedule, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings.
 Test data: Test staff user 'cashier_qa'. Work order ready to invoice; open invoice.
 Permission under test: WO View + Invoicing View/Edit + See Financial Data ON, AP/AR OFF, no delete | Original type: Combination | Dependency mode: Financial gate: confirm modal</t>
@@ -11037,7 +11259,7 @@
 4. Confirm Invoicing Delete and View and Manage AP/AR Data remain OFF.
 5. Save the role, then go Administration &gt; Staff &gt; open the test user &gt; assign role 'Cashier' &gt; Create.
 6. In a separate browser, log in as the test staff user.
-7. POSITIVE: Open a work order (view), open Invoicing, create/edit an invoice, view financial totals.
+7. POSITIVE: Open a work order (view), open Invoicing, create/edit an invoice, view financial totals INSIDE the WO detail / invoicing screen (financial figures are not on the WO list).
 8. NEGATIVE (aggregate): Attempt to delete an invoice; look for AP/AR actions; edit a WO; check nav for Customers/Schedule/Parts/Reports/Administration.</t>
         </is>
       </c>
@@ -11049,7 +11271,7 @@
 Step 4: Invoicing View+Edit ON, Delete OFF, View and Manage AP/AR Data OFF, See Financial Data ON.
 Step 5: Role saved with exactly the configured toggles. Staff assignment saved. A role change forces the affected user to be logged out.
 Step 6: Login succeeds; the user sees only navigation permitted by the assigned role.
-Step 7: WO viewable; invoice can be viewed and edited; financial totals displayed.
+Step 7: WO viewable; invoice can be viewed and edited; financial totals displayed inside the WO detail / invoicing screen. [Verification location per VIU-29: See-Financial-Data effects manifest in WO detail / invoicing, not the WO list.]
 Step 8: Invoice delete unavailable; no AP/AR actions; WO not editable; Customers, Schedule, Parts, Reports, Administration hidden.
 Overall: Cashier can view WOs and view/edit invoices with financial data. Invoicing Edit triggered the financial modal (See Financial Data ON) and cascaded View. No delete, no AP/AR, no other areas.
 VIU status: Spec: SV-7388 Invoicing financial gate; CRUD cascade; Invoicing Delete requires AP/AR. VERIFIED (staging 2026-07-01) — DISCREPANCY; see VIU-11</t>
@@ -11084,7 +11306,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Reports (all-or-nothing); See Financial Data; View and Manage AP/AR Data. OFF: everything else — all Work Orders/WO Lines/Customers/Schedule/Invoicing/Parts Department/Part Sales/Catalog/Vendor CRUD, Timesheets, History Logs, Settings, App Settings.
 Test data: Test staff user 'analyst_qa'. Reports with financial figures exist.
 Permission under test: Reports ON + See Financial Data ON + View and Manage AP/AR Data ON, all operational CRUD OFF | Original type: Combination | Dependency mode: None</t>
@@ -11143,7 +11365,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View, Edit; Work Order Lines &gt; View, Edit, Delete; Customers &gt; View, Edit; Schedule &gt; View, Edit; Invoicing &gt; View, Edit; WO sub-settings Review, Pick Parts, Order; See Financial Data. OFF: everything else — WO Delete, Customers Delete, Schedule Delete, Invoicing Delete, View and Manage AP/AR Data, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings.
 Test data: Test staff user 'svcwriter_qa'. Work order with lines, customer, schedule entry, invoice.
 Permission under test: WO V/E, WO Lines V/E/D, Customers V/E, Schedule V/E, Invoicing V/E, Review/Pick/Order ON, Financial ON, AP/AR OFF | Original type: Combination | Dependency mode: Multiple</t>
@@ -11208,7 +11430,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View, Edit; Work Order Lines &gt; View, Edit; Customers &gt; View, Edit; Schedule &gt; View, Edit; Invoicing &gt; View, Edit; Parts Department (parent); Catalog &gt; View, Edit; Vendor &gt; View, Edit; Part Sales &gt; View, Edit; WO sub-settings Review, Pick Parts, Order; See Financial Data; View and Manage AP/AR Data; Reports. OFF: every Delete (WO, WO Lines, Customers, Schedule, Invoicing, Catalog, Vendor, Part Sales); Timesheets; History Logs; Settings; App Settings.
 Test data: Test staff user 'shopmgr_qa'. Records across all covered areas.
 Permission under test: Broad View+Edit across areas, NO Delete anywhere, See Financial Data ON, View and Manage AP/AR Data ON | Original type: Combination | Dependency mode: Multiple</t>
@@ -11271,7 +11493,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Timesheets &gt; View, Edit; Work Orders &gt; View. OFF: everything else — Timesheets Delete, WO Edit/Delete, WO Lines, Customers, Schedule, Invoicing, See Financial Data, Parts Department, Part Sales, Catalog, Vendor, Reports, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'timekeeper_qa'. Timesheet entries and a work order.
 Permission under test: Timesheets View/Edit + WO View, financials OFF | Original type: Combination | Dependency mode: Cascade: auto-enable lower</t>
@@ -11330,7 +11552,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View; Invoicing &gt; View; History Logs; Reports; See Financial Data; View and Manage AP/AR Data. OFF: everything else — all Edit/Delete toggles, WO Lines, Customers, Schedule, Parts Department, Part Sales, Catalog, Vendor, Timesheets, Settings, App Settings.
 Test data: Test staff user 'auditor_qa'. Work orders, invoices, history log entries, reports.
 Permission under test: WO View + Invoicing View + History Logs ON + Reports ON + See Financial Data ON, no edits/deletes, AP/AR ON | Original type: Combination | Dependency mode: Financial gate: confirm modal</t>
@@ -11456,7 +11678,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: Intended: Invoicing &gt; View, Edit only. After resolving the financial gate: See Financial Data ON. OFF: everything else — Invoicing Delete, View and Manage AP/AR Data, Work Orders, WO Lines, Customers, Schedule, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings.
 Test data: Test staff user 'rnd1_qa'. One open invoice.
 Permission under test: Invoicing View/Edit; See Financial Data enabled via modal; nothing else | Original type: Dependency | Dependency mode: Financial gate: confirm modal</t>
@@ -11515,7 +11737,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: Intended (invalid): Part Sales &gt; View with Parts Department OFF. Expected resolvable state: Part Sales child is hidden/unsavable while parent OFF. If any usable role saved, it is with Parts Department OFF and NO parts child accessible. OFF: everything else.
 Test data: Test staff user 'rnd2_qa'.
 Permission under test: Attempt Part Sales View with Parts Department OFF (unusable combo) | Original type: Negative | Dependency mode: Parent gate: hide children</t>
@@ -11570,7 +11792,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: Intended: Work Orders &gt; Delete only. After cascade: Work Orders &gt; View, Edit, Delete all ON. OFF: everything else — WO Lines, Customers, Schedule, Invoicing, See Financial Data, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'rnd3_qa'. A deletable work order.
 Permission under test: WO Delete requested → WO View+Edit+Delete saved; nothing else | Original type: Dependency | Dependency mode: Cascade: auto-enable lower</t>
@@ -11583,7 +11805,7 @@
 3. Verify the saved role state before assigning.
 4. Save the role, then go Administration &gt; Staff &gt; open the test user &gt; assign role 'RND WO-Cascade' &gt; Create.
 5. In a separate browser, log in as the test staff user.
-6. POSITIVE: Open Work Orders; view, edit, and delete a work order.
+6. POSITIVE: Open Work Orders; view, edit, and delete a work order. Confirm the delete control (per-row delete on the list and/or inside the WO detail) is present and works.
 7. NEGATIVE (aggregate): Check nav for WO Lines actions, Customers, Schedule, Invoicing, Parts, Reports, Administration; check for financials.</t>
         </is>
       </c>
@@ -11594,7 +11816,7 @@
 Step 3: Saved role has WO View+Edit+Delete ON; no other toggle ON. No financial modal (WO not financial-gated).
 Step 4: Role saved with exactly the configured toggles. Staff assignment saved. A role change forces the affected user to be logged out.
 Step 5: Login succeeds; the user sees only navigation permitted by the assigned role.
-Step 6: All three WO operations succeed (cascade granted View+Edit alongside Delete).
+Step 6: All three WO operations succeed (cascade granted View+Edit alongside Delete); the per-row delete action is available. [Verification location per VIU-29: delete/edit effects are confirmed via the per-row delete and inside the WO detail.]
 Step 7: No WO Lines edit (separate area, not enabled), and all other areas hidden; no financial data shown.
 Overall: Requesting only WO Delete produced a saved role with WO View+Edit+Delete via cascade. User can fully manage WOs; nothing else is accessible.
 VIU status: Spec: SV-7388 CRUD cascade Delete→Edit→View. VERIFIED (staging 2026-07-01) — MATCH; see VIU Findings Log</t>
@@ -11629,7 +11851,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Parts Department (parent); Catalog &gt; View, Edit, Delete; Vendor &gt; View, Edit. OFF: everything else — Vendor Delete, Part Sales (all), See Financial Data, Work Orders, WO Lines, Customers, Schedule, Invoicing, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'rnd4_qa'. Catalog items and vendors.
 Permission under test: Parts Dept ON + Catalog V/E/D + Vendor V/E; everything else OFF | Original type: Combination | Dependency mode: Multiple</t>
@@ -11690,7 +11912,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Work Orders &gt; View; Schedule &gt; View, Edit; Timesheets &gt; View; Reports; History Logs. OFF: everything else — WO Edit/Delete, WO Lines, Schedule Delete, Timesheets Edit/Delete, Customers, Invoicing, See Financial Data, Parts Department, Part Sales, Catalog, Vendor, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'rnd5_qa'. WOs, schedule entries, timesheets, reports, history entries.
 Permission under test: WO View + Schedule V/E + Timesheets View + Reports ON + History Logs ON, financials OFF | Original type: Combination | Dependency mode: Cascade: auto-enable lower</t>
@@ -11749,7 +11971,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: Intended: Invoicing &gt; Delete. After gates resolved: Invoicing View+Edit+Delete ON, See Financial Data ON, View and Manage AP/AR Data ON. OFF: everything else — Work Orders, WO Lines, Customers, Schedule, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, Settings, App Settings.
 Test data: Test staff user 'rnd6_qa'. A deletable invoice.
 Permission under test: Invoicing V/E/D requiring See Financial Data + View and Manage AP/AR Data; nothing else | Original type: Dependency | Dependency mode: Multiple</t>
@@ -11810,7 +12032,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Settings; App Settings; Work Orders &gt; View. OFF: everything else — WO Edit/Delete, WO Lines, Customers, Schedule, Invoicing, See Financial Data, Parts Department, Part Sales, Catalog, Vendor, Reports, Timesheets, History Logs, View and Manage AP/AR Data.
 Test data: Test staff user 'rnd7_qa'.
 Permission under test: Settings ON + App Settings ON (enables managing Roles/Staff) + WO View; everything else OFF | Original type: Combination | Dependency mode: Multiple</t>
@@ -11869,7 +12091,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user.
+          <t>Logged in as an Administrator with full access. Application is on the Custom Roles &amp; Permissions build (Epic SV-7388, SV-7500 enabled). At least one test staff member exists to receive the role. A second browser/session is available to log in as the test staff user. NOTE (permission propagation): after assigning the role, log out and log back in as the user (fresh login) so the new permissions load; allow a brief settle before verifying.
 Role setup: ON: Customers &gt; View, Edit, Delete; Work Order Lines &gt; View, Edit; Parts Department (parent); Vendor &gt; View; View Mode = Full (UX only). OFF: everything else — Work Orders View/Edit/Delete, WO Lines Delete, Catalog (all), Part Sales (all), Vendor Edit/Delete, Schedule, Invoicing, See Financial Data, Reports, Timesheets, History Logs, Settings, App Settings, View and Manage AP/AR Data.
 Test data: Test staff user 'rnd8_qa'. Customers, a work order with lines, vendors.
 Permission under test: Customers V/E/D + WO Lines V/E + Parts Dept ON + Vendor V; Full View mode; financials OFF | Original type: Combination | Dependency mode: Multiple</t>

--- a/custom-roles-test-cases.xlsx
+++ b/custom-roles-test-cases.xlsx
@@ -14,6 +14,10 @@
     <sheet name="Combination - Representative" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Combination - Random" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Digital Inspections" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Run Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Passed" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Failed" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Blocked (Not Verified)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VIU Findings Log'!$A$1:$G$32</definedName>
@@ -22,6 +26,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Combination - Representative'!$A$1:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Combination - Random'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Digital Inspections'!$A$1:$H$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Passed'!$A$1:$F$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Failed'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Blocked (Not Verified)'!$A$1:$E$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +51,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -91,6 +102,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -472,19 +490,19 @@
           <t>ShopView Custom Roles &amp; Permissions — Test Suite Index</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Epic: SV-7388 (Custom Roles and Permissions)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -492,19 +510,19 @@
           <t>Verification status: VIU (Verify-in-UI) pass 3 complete — per-role verified as the restricted Tech user (tech@shopview.com) on staging, 2026-07-01. 31 findings logged (21 MATCH / 10 DISCREPANCY) — see the 'VIU Findings Log' tab. Pass 2 (live admin session) confirmed exact Custom Roles labels, the silent CRUD cascade, the 'Enable See Financial Data?' popup, and the kebab-menu variants. Pass 3 logged in AS Tech and verified all 11 per-role gate configs behave PER SPEC: CRUD gating (View-only read-only/no New; +Create&amp;Edit shows New; +Delete per-row delete), page-access nav gating (Reports/Customers/combination exact), Settings routes under '/administration', and view-mode/parts/financial effects carried in the permission wrapper (effects inside the WO detail / invoicing). Discrepancies/limits logged: '/settings' 404s (admin lives at '/administration'), a zero-permission role is not creatable (min 1 permission enforced), and permission changes require the user to re-login + settle. Earlier build-vs-spec discrepancies still stand (doubled '/api/api/sso/check' path, no unsaved-changes guard on Create Role X-close, silent-cascade vs confirmation-popup dependency-UX inconsistency). 108 test cases now VERIFIED (91 MATCH / 17 DISCREPANCY); remaining cases are UNVERIFIED — VIU pending.</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Standard column format (test-case tabs): Title | Section | Type | Priority | Preconditions | Steps | Expected Result | References</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -519,52 +537,52 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Single Permission</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="7" t="n">
         <v>117</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Template Edit</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="7" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Combination - Representative</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="7" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Combination - Random</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="7" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Digital Inspections</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="7" t="n">
         <v>121</v>
       </c>
     </row>
@@ -579,6 +597,1903 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Area/Section</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Difference/Notes</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-005</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing Delete requires Manage AP/AR (AP/AR gate)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing Delete cannot be applied without View and Manage AP/AR Data; the AP/AR gate enforces enabling View and Manage AP/AR Data (in addition to the financial gate).</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Admin role editor with See Financial Data ON and AP/AR OFF: enabling Invoicing 'Delete / Reverse' checked View+Create&amp;Edit+Delete but did NOT trigger any 'View and Manage AP/AR Data' gate modal and left AP/AR unchecked. Expected an AP/AR gate enforcing AP/AR enablement.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>AP/AR editor gate for Invoicing Delete did not fire (financial gate works, AP/AR gate absent). Deviates from expected.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>DI-111</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Step 1: Login succeeds.
+Step 2: Work Orders are not accessible to this role.
+Step 3: Inspections cannot be reached - no Work Orders access.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock role DOES grant workOrdersView -&gt; Work Orders ARE accessible in the Tech UI (landed on /workorders, WO list rendered). Existing inspections on a line are therefore reachable/visible (read-only, since role lacks Work Order Lines rights). This CONTRADICTS the expected "no Work Orders access".</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT FINDING: the live "Time Clock" system role includes workOrdersView (description says "Clock in/out only"), so it has WO access, unlike the spec precondition. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>DI-117</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Step 2: Not applicable - no Work Orders access, statuses cannot be seen.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Work Orders ARE accessible for Time Clock (has workOrdersView), so inspection status labels CAN be seen - contradicts expected "no Work Orders access, statuses cannot be seen".</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT FINDING: Time Clock role grants workOrdersView -&gt; WO access exists. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Area/Section</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Reason Blocked</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-005</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Customer Delete grants delete of customer records only (not payments)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Tech role [customersView,customersCreateAndEdit,customersDelete]: create affordance present ('New customer'); customer-delete control was not surfaced on the customers list or the opened customer detail sub-tab via automated scan. Customer Delete permission + cascade confirmed in the role editor.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Delete affordance not located via automated scan (list/detail); permission exists and cascades in editor. Delete not executed per safety.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-006</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Sensitive customer fields gated by Manage AP/AR, not Customer permission</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Verifying that sensitive customer fields are gated specifically by View+Manage AP/AR Data (independent of Customer View) requires identifying the exact AP/AR-gated fields in the customer detail and comparing renders with/without seeApArData; not reliably determinable via automated scanning in this session.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AP/AR field-gating not reliably verifiable via automated UI scan; needs targeted field-level manual check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-005</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales Delete grants delete sales and reverse part-sale invoices</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Tech role [partSalesView,partSalesCreateAndEdit,partSalesDelete]+financial: create affordance present ('New part sale'); part-sale delete/reverse control not surfaced on list or opened part-sale detail via automated scan. Part Sales Delete permission confirmed in role editor.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Delete/reverse affordance not located via automated scan; permission exists in editor. Not executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>SP-CAT-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Catalog &amp; Inventory Delete grants delete parts from catalog</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Catalog &amp; Inventory</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Tech role [catalogInventoryView,CreateAndEdit,Delete]: create affordance present ('New catalog part'); catalog-part delete control not surfaced on list row menu or opened catalog detail via automated scan. Catalog Delete permission confirmed in role editor.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Delete affordance not located via automated scan; permission exists in editor. Not executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>SP-VEND-004</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Mgmt Delete grants delete vendors and POs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Vendor &amp; Order Management</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Tech role [vendorOrderManagementView,CreateAndEdit,Delete]: create affordance present ('New vendor'); vendor/PO delete control not surfaced on list or opened vendor detail sub-tab via automated scan. Vendor Delete permission confirmed in role editor.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Delete affordance not located via automated scan; permission exists in editor. Not executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing Delete grants delete payments, void transactions, delete part-sale return</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Tech role [...invoicingPaymentsDelete]+financial+AP/AR: WO Finance tab rendered but the available WO was an estimate with no invoice/payments, so delete-payment/void controls had nothing to act on and were not surfaced. Invoicing Delete permission confirmed in role editor.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Delete-payment/void affordance requires an invoiced WO with payments (not available among test WOs); not executed per safety.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Cross-dep: deleting a customer payment needs Invoicing Delete (Customer Delete alone insufficient)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Cross-dependency (Customer Delete alone cannot delete a customer payment; Invoicing Delete required). Confirming requires attempting a real customer-payment deletion, which is a destructive action that must not be executed.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Not verifiable without executing a prohibited destructive delete; affordance-absence alone cannot prove the dependency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cross-dep: reversing an invoice needs WO Delete even with Invoicing Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Cross-dependency (invoice reversal requires WO Delete even with Invoicing Edit). Confirming requires attempting a real invoice reversal, which is a destructive action that must not be executed.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Not verifiable without executing a prohibited destructive reversal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-001</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Review Work Orders GRANT — Review option available with WO View + Review</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Review GRANT perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-002</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Review Work Orders WITHHOLD — Review option absent when toggle OFF</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Review WITHHOLD perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-004</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Pick Parts GRANT — can pick parts from inventory onto WO line</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Pick GRANT perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-005</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pick Parts WITHHOLD — pick action blocked/absent when toggle OFF</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Pick WITHHOLD perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-007</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Order Parts GRANT — place PO for parts on WO and receive deliveries</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Order GRANT perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-008</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Order Parts WITHHOLD — cannot place PO or receive parts when OFF</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact Order WITHHOLD perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-010</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>WO sub-settings are INDEPENDENT — enabling one does not enable others</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact independence perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-011</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Return part from WO line requires NO permission (note case)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Role PUT+assign+fe-permissions hydration succeeded with the exact return part no-perm perm set; WO detail rendered, but the Review/Pick/Order/Return actions live inside per-WO-line kebab menus and depend on WO/part workflow state, so the action-level affordance was not statically observable within run budget.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Permission set correctly applied &amp; hydrated; deep line-level action not automatable non-destructively here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>SP-CPORT-001</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Customer Portal GRANT — access and manage customer portal config</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Portal</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>customerPortalPageAccess hydrated ON, but no Customer Portal nav item appears and /customer-portal, /customer-portal/settings, /administration/customer-portal all return the 404 page — no reachable customer-portal management surface exists for this role in the staging build.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Grant not verifiable: portal page/route not exposed in build even when permission ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>SP-BPORT-001</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Billing Portal GRANT — access and manage billing portal</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Billing Portal</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>billingPortalPageAccess hydrated ON, but no Billing Portal nav item appears and /billing-portal, /billing-portal/settings, /administration/billing-portal all return the 404 page — no reachable billing-portal surface exists for this role in the staging build.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Grant not verifiable: portal page/route not exposed in build even when permission ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>SP-PDEPT-004</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Parts Department PRESERVES child settings — OFF then back ON restores prior CRUD</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Parts Department</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>The role editor toggle grid is virtualized and re-renders inconsistently between loads, so the multi-step off-&gt;on preserve-child-settings interaction could not be driven reliably within the 2-try budget without risking a bad save.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Editor preserve-settings interaction not reliably automatable here (non-destructive limit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-003</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Settings parent DEPENDENCY — subs hidden via slide in editor when parent OFF</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>In this build the role editor renders "Settings" as a single Page-Access toggle rather than a Settings parent group with slide-in sub-rows, so the specified sub-setting slide-hide behaviour is not present/verifiable in the editor as written.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Editor exposes single Settings toggle, not a sub-slide group (build).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-010</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Integrations sub GRANT — manage QuickBooks, IBS, and Open API</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>No settingsIntegrations permission exists in the fe-permission catalog and no Integrations sub-setting is present in the role editor (per build); QuickBooks/IBS are governed under Finance (IBS) and a top-level integration flow, not a distinct Integrations toggle — so this grant case is not applicable/verifiable as specified.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>No Integrations sub-setting in this build (documented).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-011</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Integrations sub WITHHOLD — area hidden/blocked when settingsIntegrations OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>No settingsIntegrations permission exists and no Integrations sub-setting is present in the role editor (per build); the withhold case is not applicable/verifiable as specified.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>No Integrations sub-setting in this build (documented).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-016</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>View/Manage Wages sub GRANT — manage view/manage employee wage rates (sensitive)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>settingsWages ON in isolation lands the user on /home with no Administration section (wages is a sensitive field surfaced within Staff/Wages rather than a standalone nav section), so wage-management access could not be verified in isolation without settingsApp.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Wages is an in-Staff sensitive field, not a standalone section — not verifiable alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-003</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — No tech time field is shown</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Tech view is active (Total Tech Hours shown, no Approve). Whether a separate editable "tech time field" input is hidden is a line-level form detail not distinguishable from the WO-detail scan.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Line-level field visibility not statically observable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-005</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — Cannot Send to Portal</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>A "Send to Portal" affordance was not located in either Full or Tech WO-detail scans (likely nested in an overflow/more menu), so the tech-view restriction could not be confirmed.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Send-to-Portal control not located in scan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-006</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — Cannot view labor rates</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Labor-rate visibility could not be isolated to view mode in the WO-detail scan (labor rate is also gated by See Financial Data), so the tech-only restriction was not cleanly observable.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Labor-rate visibility not cleanly isolated to view mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-007</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — Limited parts request form</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>The tech-limited parts-request form is a modal reached through the parts add flow and was not opened non-destructively within budget.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Parts-request form modal not opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-008</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — Cannot edit existing WO lines (create-only)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Tech view allows creating new lines (New Line present); the create-only vs edit-existing distinction requires editing an existing line inline and observing block, which was not automatable non-destructively.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Edit-existing-line restriction not statically observable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-009</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — WO lines read-only after approval</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>The "lines read-only after approval" state requires a line in approved state and an edit attempt; not observable without mutating data.</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Post-approval read-only state not observable non-destructively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-010</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Send to Portal appears only in Full View (not Tech) — comparison</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Comparison hinges on the "Send to Portal" control, which was not located in Full or Tech WO-detail scans (overflow menu); could not confirm presence-in-full / absence-in-tech.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Depends on unlocated Send-to-Portal control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-004</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Financial gate — enabling Part Sales CRUD while Financial OFF triggers confirm modal</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Triggering the financial confirm modal requires toggling Part Sales CRUD in the virtualized role-editor grid; the editor re-renders inconsistently and the modal could not be triggered/observed reliably within the 2-try, non-destructive budget.</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Editor confirm-modal interaction not reliably automatable here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-005</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Financial gate — enabling Invoicing CRUD while Financial OFF triggers confirm modal</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Same as SP-FIN-004: the Invoicing-CRUD financial confirm modal is an editor interaction not reliably drivable in the virtualized editor grid within budget.</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Editor confirm-modal interaction not reliably automatable here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-006</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Security — no financial leak in Receive Part modal when Financial OFF (SV-7973)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Regression check requires opening the Receive Part modal on a WO PO line (Order Parts ON, Financial OFF) and inspecting it for financial leakage; the modal is reached through a stateful parts-receiving flow not automatable non-destructively here. Role hydrated correctly (seeFinancialData OFF, woOrderParts ON).</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Receive Part modal not opened non-destructively (SV-7973 guard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>SP-APAR-001</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Manage AP/AR GRANT — Unpaid/Payments/Credits tabs, aging reports, bulk payments</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Manage AP/AR</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>seeApArData hydrated ON, but the AP/AR surface (Unpaid/Payments/Credits tabs, aging, bulk payments) lives under Invoicing, and /invoicing returns 404 for this role set in staging — the AP/AR UI was not reachable to confirm the tabs/reports.</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>AP/AR UI (invoicing) not reachable in build to verify grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>SP-APAR-002</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Manage AP/AR WITHHOLD — tabs, aging reports, and bulk payments hidden when OFF</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Manage AP/AR</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>seeApArData OFF, but the Invoicing/AP-AR surface is unreachable (/invoicing 404) for this role set, so the hidden-vs-shown distinction for AP/AR tabs could not be observed.</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>AP/AR UI unreachable to verify withhold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>SP-APAR-003</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Manage AP/AR sensitive customer fields — Edit Customer modal + Customer Overview panel</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Manage AP/AR</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Verifying sensitive customer fields requires opening the Edit Customer modal and Customer Overview panel and diffing fields between apar ON/OFF roles; the field-level modal diff was not automatable non-destructively within budget.</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Edit-Customer modal field diff not automatable here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>SP-APAR-005</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Manage AP/AR does NOT gate CRUD, but Invoicing Delete additionally requires it</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Manage AP/AR</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Confirming that Invoicing Delete additionally requires AP/AR (while general CRUD does not) requires attempting an invoice delete, which is destructive and out of scope; the invoicing UI is also unreachable for this role.</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Invoice-delete gating not verifiable non-destructively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>SP-HIST-001</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>View History Logs GRANT — history/audit logs shown app-wide</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View History Logs</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>viewHistoryLogs hydrated ON, but no History/Audit-log affordance was located on the WO detail or Parts/Inventory pages scanned (history/audit logs are surfaced in entity-specific panels/modals not reached by the scan), so app-wide visibility could not be confirmed.</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>History-log UI not located in scanned pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>SP-HIST-002</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>View History Logs WITHHOLD — history/audit logs hidden app-wide when OFF</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View History Logs</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>viewHistoryLogs OFF; as with HIST-001 no history/audit affordance was located in the scanned pages to confirm hidden-vs-shown.</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>History-log UI not located in scanned pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>TE-ADMIN-001</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Administrator: cannot be edited to lose Administration-pages access</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Administrator</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Choosing the Administrator template pre-fills the editor with all 42 permissions and shows a guard banner: "Full administrative access - This role has every permission enabled, giving it full administrative access. Make sure this is intended before saving." No discrete "Access Administration pages" permission exists in the catalog (settings access is split across settingsApp/Service/Finance/Parts/Wages/DataImport), so the specific locked/revert toggle described could not be located or exercised.</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Template-apply pre-fill from Administrator verified (all perms enabled + full-admin guard banner, footer button labelled "Create"). The exact "Admin-pages access" lock/revert-on-save behavior is not represented as a single toggle in this build; not confirmable without a matching permission. 2 focused editor attempts made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>TE-SM-005</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager: enable Timesheets &gt; Delete</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Manager</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>No 'Timesheets Delete' permission exists in the product. The fe-permissions catalog (42 perms) exposes only timesheetsView and timesheetsCreateAndEdit for Timesheets - there is no timesheetsDelete toggle to enable.</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Unverifiable: the Timesheets group has no Delete permission in the product, so the described toggle cannot be set. Likely test-case/spec defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>DI-003</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>DI-005</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>DI-006</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>DI-014</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>DI-016</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>DI-017</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>DI-025</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>DI-027</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>DI-028</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>DI-036</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>DI-038</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>DI-039</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>DI-047</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>DI-049</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>DI-050</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>DI-058</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Technician - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>DI-060</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Technician - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>DI-061</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Technician - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>DI-069</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "add multiple templates + 4th-limit" requires destructively adding 3-4 real inspections to a shared staging work-order line (and the 4th-limit is an unresolved VIU in the spec). Capability confirmed: role has workOrderLinesCreateAndEdit (add is permitted).</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive mutation of shared staging data + spec VIU (max-per-line unspecified). Add-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>DI-071</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Completing an inspection (fill all required fields -&gt; Submit and Generate Report) is destructive: it submits, generates a PDF report and flips status to Completed on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: destructive (generates real PDF report / status change on shared staging). Submit-capability confirmed via permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>DI-072</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED. Verifying "100% filled but not submitted still shows Open" requires filling a real inspection to 100% on shared staging data. Capability confirmed: role has workOrderLinesCreateAndEdit.</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED reason: requires destructive fill of a real inspection to 100% on shared staging. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17671,4 +19586,7789 @@
   <autoFilter ref="A1:H122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ShopView Custom Roles &amp; Permissions — Live Test Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Run date: 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Environment: staging (Foothills Group Inc), per-role as Tech via dev-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Overall Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Per-Batch Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Batch A</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>43</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Batch B</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>34</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Batch C</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Batch D</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Batch E</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>98</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>232</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Run Discrepancies (see VIU Findings Log VIU-32..37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-32 [SP-INV-005, FAIL]: Invoicing Delete with See Financial Data ON but View/Manage AP/AR OFF does NOT trigger the AP/AR dependency gate/modal (financial gate works; AP/AR gate missing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-33 [DI-111 / DI-117, FAIL]: The 'Time Clock' system role grants workOrdersView, so Time-Clock users reach Work Orders / Digital Inspections read-only — contradicts its clock-in/out-only intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-34: CRUD dependency cascade is UI-editor-only, NOT server-enforced — a direct API PUT of a Delete/Edit permission without its View parent is accepted by the backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-35: /administration/inspection-templates route lacks a settingsService guard — reachable read-only via direct URL by roles holding any other settings sub-permission (the Settings&gt;Service menu path is correctly denied).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-36: Several granted surfaces return 404 in this build even when the permission is granted (Customer/Billing Portal, some Invoicing/AP-AR pages) — grant path reaches a 404 rather than the feature (possible build gap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>• VIU-37 [VERIFIED, informational]: Setting view_mode full/tech auto-adds a woFullViewMode / woTechViewMode marker permission to the stored role.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F233"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Area/Section</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Actual (brief)</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>WO View grants Work Orders nav and read-only WO access</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>WO View grants read-only WO access; no create control.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>WO View OFF hides Work Orders nav and blocks direct URL</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>WO nav hidden; direct URL blocked (nav-hidden re-corroborated 2026-07-02 via reports-only role)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>WO Edit grants create/edit of WO fields (asset, advisor, tech, status)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>WO Edit grants create/edit; New present.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>WO Edit OFF blocks create/edit while View remains read-only</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>WO Edit OFF -&gt; read-only, no create/edit.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>WO Delete grants delete WO and invoice reversal (no payments)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>WO Delete grants delete affordance (WO-detail action menu present); not executed per safety.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>WO Delete OFF hides delete and blocks invoice reversal</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>WO Delete OFF -&gt; delete affordance absent.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>WO cascade: enabling Edit auto-enables View</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Cascade Edit-&gt;View confirmed in role editor.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>WO cascade: enabling Delete auto-enables Edit and View</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Cascade Delete-&gt;Edit+View confirmed.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>WO reverse-cascade: disabling View auto-disables Edit and Delete</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Reverse-cascade View OFF -&gt; Edit+Delete OFF confirmed.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>SP-WO-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>WO reverse-cascade: disabling Edit auto-disables Delete</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Orders</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Reverse-cascade Edit OFF -&gt; Delete OFF, View retained.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOL-001</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>WOL Edit grants line/part/inspection editing on WOs</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Order Lines</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>WOL Edit grants add/edit lines.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOL-002</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>WOL Edit OFF blocks line editing (view-only WO lines)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Order Lines</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>WOL Edit OFF -&gt; lines view-only.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOL-003</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>WOL Delete grants line removal and inspection reopen/remove</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Order Lines</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>WOL Delete grants line-removal affordance (row menu); not executed.</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOL-004</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>WOL editor blocks WOL Edit while WO View is OFF (SV-7981)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Work Order Lines</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>WOL Edit cannot be enabled while WO View OFF (SV-7981) confirmed via editor gate modal.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>SP-SCH-001</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Schedule View grants calendar/appointments/tech assignments (all techs)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Schedule</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>RE-VERIFIED: prior FAIL was a false negative (old client-injection harness + guard race). Schedule View alone grants read-only calendar.</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>SP-SCH-002</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Schedule View OFF hides Schedule nav and blocks direct URL</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Schedule</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Schedule nav hidden; direct URL blocked (nav-hidden re-corroborated 2026-07-02 via reports-only role)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>SP-SCH-003</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Schedule Edit grants create/modify appointments, tech assign, drag-and-drop</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Schedule</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>RE-VERIFIED: prior FAIL was a false negative. Calendar renders with edit permission.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>SP-SCH-004</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Schedule Delete grants remove appointments; reverse-cascade check</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Schedule</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Schedule Delete affordance + cascade/reverse-cascade confirmed.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-001</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Customer View grants customer records/contacts/vehicles/history</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Customer View grants read-only customer access.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-002</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Customer View OFF hides Customers nav and blocks direct URL</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Customers nav hidden; direct URL blocked (nav-hidden re-corroborated 2026-07-02 via reports-only role)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-003</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Customer Edit grants create/edit customers, contacts, vehicles and New-WO Add buttons</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Customer Edit grants create/edit + New-WO Add buttons.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>SP-CUST-004</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Customer Edit OFF hides Add Customer/Add Asset in New WO flow</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Management</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Customer Edit OFF: no Add Customer (New absent)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run as Tech 2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-001</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales View grants part sales records/returns/transactions (parent+financial on)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>RE-VERIFIED: prior FAIL was a false negative. Part Sales View grants read-only part-sales records.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-002</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales financial gate: enabling CRUD while Financial OFF triggers confirm modal</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales CRUD financial confirm modal confirmed.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-003</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales parent gate: unavailable when Parts Department OFF</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales gated behind Parts Department parent.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-004</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales Edit grants create sales/returns and process transactions</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales Edit grants create.</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>SP-PS-006</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales not reachable via direct URL without access (SV-7965)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Part Sales</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Part Sales not reachable via direct URL without access (SV-7965); redirected away.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>SP-CAT-001</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Catalog &amp; Inventory View grants catalog/inventory/stock/history browsing</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Catalog &amp; Inventory</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Catalog View grants read-only catalog/inventory browsing.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>SP-CAT-002</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Catalog &amp; Inventory parent gate: unavailable when Parts Department OFF</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Catalog &amp; Inventory</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Catalog gated behind Parts Department parent.</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>SP-CAT-003</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Catalog &amp; Inventory Edit grants catalog edits, adjustments and cycle counts</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Catalog &amp; Inventory</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Catalog Edit grants catalog edits.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>SP-CAT-005</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Catalog &amp; Inventory View OFF blocks catalog browsing (with parent on)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Catalog &amp; Inventory</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Catalog View OFF blocks catalog browsing/direct URL even with Parts Department on.</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>SP-VEND-001</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Mgmt View grants vendors/POs/deliveries/part history/return requests</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Vendor &amp; Order Management</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Vendor View grants read-only vendor/PO access.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>SP-VEND-002</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Mgmt parent gate: unavailable when Parts Department OFF</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Vendor &amp; Order Management</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Vendor gated behind Parts Department parent.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>SP-VEND-003</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Mgmt Edit grants vendor/PO/delivery/invoice/return operations</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Vendor &amp; Order Management</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Vendor Edit grants vendor/PO operations.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-001</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing View grants invoice view and Finance tab access</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing View grants Finance tab + invoice view.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-002</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing View OFF but Financial ON: pricing visible, no direct invoice access</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing View OFF + Financial ON -&gt; pricing visible, no direct invoice access.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-003</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing financial gate: enabling CRUD while Financial OFF triggers confirm modal</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing CRUD financial confirm modal confirmed.</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>SP-INV-004</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing Edit grants create invoices, payments, deposits, Send to Terminal</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Invoicing &amp; Payments</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Invoicing Edit grants create invoices/deposits (Send to Terminal in payment flow); no delete/void present.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>SP-TS-001</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets View grants viewing timesheets from WOs; Timesheets nav visible</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Timesheets</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets View grants read-only timesheets access (page reachable).</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>SP-TS-002</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets View OFF hides nav, but Reports ON still shows timesheet activities report</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Timesheets</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets nav hidden but timesheet-activities report available via Reports.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>SP-TS-003</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Clock in/out always available regardless of Timesheets permission</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Timesheets</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Clock in/out available regardless of Timesheets permission.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>SP-TS-004</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets Edit grants entry edits, hour adjustments, attendance for all staff</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Timesheets</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets Edit role loads timesheets with no Delete action; edit affordance not exercised (no entries for this tech).</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>SP-TS-005</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets has no Delete checkbox/action (verify absence)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Timesheets</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Timesheets has no Delete checkbox in role editor.</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-003</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Review Work Orders DEPENDENCY — greyed in editor when WO View OFF</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Editor dependency confirmed: sub-toggle disabled while WO View OFF.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-006</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Pick Parts DEPENDENCY — greyed in editor when WO View OFF</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Editor dependency confirmed: sub-toggle disabled while WO View OFF.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>SP-WOSUB-009</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Order Parts DEPENDENCY — greyed in editor when WO View OFF</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; WO Sub-Settings</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Editor dependency confirmed: sub-toggle disabled while WO View OFF.</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>SP-RPT-001</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Reports GRANT — Reports nav visible and all reports accessible</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Reports</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Reports granted and accessible.</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>SP-RPT-002</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Reports WITHHOLD — nav hidden and direct URL blocked when OFF</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Reports</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Reports withheld: nav hidden, direct URL blocked.</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>SP-RPT-003</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Reports ON with Timesheets View OFF still shows timesheet activities report</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Reports</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Timesheet activities report exposed via Reports independent of Timesheets View.</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>SP-CPORT-002</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Customer Portal WITHHOLD — nav hidden and direct URL blocked when OFF</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Customer Portal</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Customer Portal withheld: nav hidden, direct URL blocked.</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>SP-BPORT-002</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Billing Portal WITHHOLD — nav hidden and direct URL blocked when OFF</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Billing Portal</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Billing Portal withheld: nav hidden, direct URL blocked.</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>SP-PDEPT-001</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Parts Department GRANT — parent ON reveals children per their CRUD</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Parts Department</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Parts Department children accessible per their View CRUD.</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>SP-PDEPT-002</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Parts Department PARENT-GATE — OFF makes all children inaccessible regardless of their CRUD</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Parts Department</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Parent-gate confirmed structurally in editor; child access is parent-gated.</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>SP-PDEPT-003</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Parts Department DEPENDENCY — children HIDDEN via slide in editor when parent OFF</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Parts Department</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Editor: child rows hidden when Parts Department parent OFF.</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-001</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Settings parent GRANT — Administration area accessible with a sub ON</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Settings parent+App ON grants Administration.</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-002</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Settings parent WITHHOLD — parent OFF hides entire Administration area and all subs</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Settings parent OFF hides whole Administration area.</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-004</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>App Settings sub GRANT — manage org info/branding, Roles &amp; Permissions management, and Staff/Workplaces management</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>App Settings manages org info, Roles &amp; Permissions, Staff/Workplaces.</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-005</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>App Settings sub WITHHOLD — area hidden/blocked when settingsApp OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>App Settings area hidden/blocked when settingsApp OFF.</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-006</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Service sub GRANT — manage labor types, canned lines, asset types, departments, and Digital Inspections</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Service sub grants labor types/canned lines/asset types/inspections.</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-007</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Service sub WITHHOLD — area hidden/blocked when settingsService OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Service area hidden/blocked when settingsService OFF.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-008</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Parts sub GRANT — manage pricing matrices, categories, and parts config</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Parts sub grants pricing matrices/categories/parts config.</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-009</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Parts sub WITHHOLD — area hidden/blocked when settingsParts OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Parts area hidden/blocked when settingsParts OFF.</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-012</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Finance sub GRANT — manage tax config and payment settings/methods</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Finance sub grants tax config and payment settings/methods.</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-013</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Finance sub WITHHOLD — area hidden/blocked when settingsFinance OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Finance area hidden/blocked when settingsFinance OFF.</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-014</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Data Import sub GRANT — manage bulk import</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Data Import sub grants bulk import.</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-015</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Data Import sub WITHHOLD — area hidden/blocked when settingsDataImport OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Data Import area hidden/blocked when settingsDataImport OFF.</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-017</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>View/Manage Wages sub WITHHOLD — area hidden/blocked when settingsWages OFF (parent ON)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Wages area hidden/blocked when settingsWages OFF.</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-018</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>App Settings gates Roles &amp; Permissions and Staff/Workplaces management</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>App Settings gates Roles &amp; Permissions and Staff/Workplaces.</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>SP-SET-019</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>View/Manage Wages is sensitive and independent from other Service/Parts subs</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Settings</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>View/Manage Wages independent from App Settings; sensitive wage data gated separately.</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-001</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Full View GRANT — all fields, approve/review/split, Send to Portal, actual Estimate</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Full View exposes all fields + approve/review actions.</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-002</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — Estimate column shows Tech Time (not actual estimate)</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Tech View shows tech time in the estimate/hours column.</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-004</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Tech View restriction — No approve action / cannot approve lines</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Tech View: no approve action.</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>SP-VM-011</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>View Mode is NOT a security boundary — financial columns governed by See Financial Data</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; View Mode</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>View Mode is not the financial boundary; See Financial Data governs $.</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-001</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>See Financial Data GRANT — pricing/costs/margins/financial columns shown app-wide</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Financial data visible with seeFinancialData ON.</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-002</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>See Financial Data WITHHOLD — ALL financial data hidden everywhere when OFF</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>All financial data hidden with seeFinancialData OFF.</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>SP-FIN-003</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>See Financial Data OFF still allows CRUD (data operations unaffected)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; See Financial Data</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Financial OFF hides $ but CRUD still allowed.</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>SP-APAR-004</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Manage AP/AR is INDEPENDENT from See Financial Data (Financial ON + AP/AR OFF)</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Single Permission &gt; Manage AP/AR</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Financial and AP/AR are independent cross-toggles (hydrated independently).</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>TE-ADMIN-002</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Administrator: remove Work Orders Delete only (delta), rest of full access intact</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Administrator</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (40 perms). Removed: WO Delete.</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>TE-ADMIN-003</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Administrator: remove History only (delta), all other access intact</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Administrator</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (40 perms). Removed: History.</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>TE-ADMIN-004</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Administrator-based role: assignment forces logout, edited role applies on next login</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Administrator</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (40 perms). Removed: Vendor Delete.</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>TE-ADMIN-005</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Administrator: template list shows only expected full-access template</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Administrator</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Verified via role-templates endpoint that backs the Choose-a-template picker.</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>TE-SM-001</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager: ADD Invoicing Delete (template lacked it), rest intact</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Manager</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (37 perms). Added: Invoicing Delete.</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>TE-SM-002</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager: REMOVE Financial access (financial confirm modal), rest intact</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Manager</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (35 perms). Removed: Financial.</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>TE-SM-003</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager: REMOVE AP/AR access (AP/AR confirm modal), rest intact</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Manager</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (35 perms). Removed: AP/AR.</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>TE-SM-004</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager: MULTI-toggle remove Reports + Settings, rest intact</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Manager</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (33 perms). Removed: Reports, Settings App, Settings Wages.</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>TE-SSA-001</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor: ADD Customers Delete, rest intact</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (33 perms). Added: Customers Delete.</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>TE-SSA-002</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor: REMOVE Work Orders Edit (reverse cascade removes Delete), rest intact</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Cascade case: resulting role set to Edit+WO Delete both OFF, View retained; Tech access matches expected. Editor enforces cascade (unchecking Edit auto-clears WO Delete). Note: a direct API PUT sending WO Delete without its Edit parent is accepted by the backend (no server-side cascade) - UI-only guard.</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>TE-SSA-003</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor: REMOVE Customer Portal, rest intact</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (31 perms). Removed: Customer Portal.</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>TE-SSA-004</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor: MULTI-toggle remove Catalog Edit + Reports, rest intact</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (30 perms). Removed: Catalog Edit, Reports.</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>TE-SADV-001</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor: ADD Work Orders Delete (cascade), rest intact</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Advisor</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (27 perms). Added: WO Delete.</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>TE-SADV-002</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor: ADD AP/AR access, rest intact</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Advisor</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (27 perms). Added: AP/AR.</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>TE-SADV-003</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor: REMOVE Part Sales Edit (view-only), rest intact</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Advisor</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (25 perms). Removed: Part Sales Edit.</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>TE-SADV-004</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor: MULTI-toggle add Timesheets Edit + AP/AR, rest intact</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Advisor</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (28 perms). Added: AP/AR, Timesheets Edit.</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>TE-FORE-001</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Foreman: ADD Part Sales Edit (template had View only), rest intact</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Foreman</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (24 perms). Added: Part Sales Edit.</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>TE-FORE-002</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Foreman: REMOVE Financial access (financial confirm modal), rest intact</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Foreman</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (22 perms). Removed: Financial.</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>TE-FORE-003</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Foreman: MULTI-toggle add WO Delete + Invoicing Delete, rest intact</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Foreman</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (25 perms). Added: Invoicing Delete, WO Delete.</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>TE-FORE-004</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Foreman: ADD Catalog Delete, rest intact</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Foreman</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (24 perms). Added: Catalog Delete.</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>TE-TECH-001</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Technician: switch TECH VIEW to FULL VIEW (delta), rest intact</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Technician</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>view_mode stored=full; woFullViewMode present, woTechViewMode absent.</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>TE-TECH-002</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Technician: ADD Work Orders Edit (cascade from View), rest intact</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Technician</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (8 perms). Added: WO Edit.</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>TE-TECH-003</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Technician: parent-gate - Order Parts hidden until Parts Dept enabled</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Technician</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Live Technician template already had History(viewHistoryLogs) ON; result unaffected.</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>TE-TECH-004</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Technician: MULTI-toggle add Financial + History, rest intact</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Technician</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Live Technician template already had History(viewHistoryLogs) ON; result unaffected.</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>TE-PM-001</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager: REMOVE Part Sales Edit (reverse cascade removes Delete), rest intact</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Manager</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Cascade case: resulting role set to Edit+Part Sales Delete both OFF, View retained; Tech access matches expected. Editor enforces cascade (unchecking Edit auto-clears Part Sales Delete). Note: a direct API PUT sending Part Sales Delete without its Edit parent is accepted by the backend (no server-side cascade) - UI-only guard.</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>TE-PM-002</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager: REMOVE Settings, rest intact</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Manager</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (28 perms). Removed: Settings DataImport, Settings Finance, Settings Parts.</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>TE-PM-003</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager: ADD Timesheets View, rest intact</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Manager</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (32 perms). Added: Timesheets View.</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>TE-PM-004</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager: MULTI-toggle remove Financial + AP/AR (both gates), rest intact</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Manager</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (29 perms). Removed: AP/AR, Financial.</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>TE-PT-001</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician: ADD Part Sales Delete, rest intact</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Technician</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (20 perms). Added: Part Sales Delete.</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>TE-PT-002</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician: REMOVE Financial access (financial confirm modal), rest intact</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Technician</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (18 perms). Removed: Financial.</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>TE-PT-003</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician: MULTI-toggle add Review Parts + Customers Delete, rest intact</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Technician</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>"Review Parts" mapped to woReviewWorkOrders (only review permission in catalog).</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>TE-PT-004</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician: REMOVE Vendor Edit (reverse cascade removes Delete), rest intact</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Parts Technician</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Cascade case: resulting role set to Edit+Vendor Delete both OFF, View retained; Tech access matches expected. Editor enforces cascade (unchecking Edit auto-clears Vendor Delete). Note: a direct API PUT sending Vendor Delete without its Edit parent is accepted by the backend (no server-side cascade) - UI-only guard.</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>TE-OFFICE-001</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Office: non-editable system template opens read-only</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Office</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed via GET /api/roles/{office} editable flag.</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>TE-SALES-001</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative: ADD Customers View/Edit (cascade), rest intact</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Sales Representative</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (6 perms). Added: Customers Edit, Customers View.</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>TE-SALES-002</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative: REMOVE Reports, rest intact</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Sales Representative</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (3 perms). Removed: Reports.</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>TE-SALES-003</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative: REMOVE Financial (financial confirm modal), rest intact</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Sales Representative</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (3 perms). Removed: Financial.</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>TE-SALES-004</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative: MULTI-toggle add Part Sales V/E + Catalog View, rest intact</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Sales Representative</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Tech effective perms match target (7 perms). Added: Catalog View, Part Sales Edit, Part Sales View.</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>TE-SADV-005</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor: REMOVE WOL Edit (reverse cascade removes Delete), rest intact</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Service Advisor</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Cascade case: resulting role set to Edit+WO Lines Delete both OFF, View retained; Tech access matches expected. Editor enforces cascade (unchecking Edit auto-clears WO Lines Delete). Note: a direct API PUT sending WO Lines Delete without its Edit parent is accepted by the backend (no server-side cascade) - UI-only guard.</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>TE-TIMECLK-001</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock: non-editable system template opens read-only</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Template Edit &gt; Time Clock</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed via GET /api/roles/{timeclock} editable flag.</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-001</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Read-only Front Desk role — view WO/Customers/Schedule, no edits, no financials</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-002</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Scheduler role — full Schedule CRUD + WO/Customers view, no financials</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-003</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Junior Tech (Tech View) — WO view, WO Lines edit, Pick Parts, no financials</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=tech. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-004</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Parts-only clerk — Parts Dept + Catalog V/E + Vendor V + Part Sales V, financials ON</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-005</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Cashier/Invoicing — WO View + Invoicing V/E + Financial ON, no AP/AR, no delete</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-006</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Reports-only analyst — Reports ON + Financial ON + AP/AR ON, all CRUD OFF</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-007</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Service writer (no AP/AR) — broad V/E across WO/Lines/Customers/Schedule/Invoicing, Financial ON</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-008</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Shop manager minus deletes — broad V/E, no Delete anywhere, Financial + AP/AR ON</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-009</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Timekeeper — Timesheets V/E + WO View, no financials</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>CB-REP-010</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Representative: Auditor — read-only across WO/Invoicing/History + Reports + Financial, no edits</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Representative)</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-001</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Random: Invoicing Edit while See Financial Data OFF — financial confirm modal fires, resolve, verify</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-002</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Random: Part Sales View with Parts Department OFF — parent gate hides/blocks child (negative)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Negative parent-gate: no valid parts child without Parts Dept; resolvable role = no parts access (empty set).; PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.; Negative parent-gate case: exercising the UI hide/greying of parts children while Parts Dept is OFF is UI-only (VERIFIED prior VIU, staging 2026-07-01). API-side resolvable role = no parts codes; Tech confirmed to have NO Parts (Catalog/Vendor/Part Sales) access; only view-mode marker present.</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-003</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Random: WO Delete-only intent — cascade auto-enables Edit+View, verify saved state</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-004</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Random: Catalog Delete + Vendor Edit + Parts Department ON — only parts-dept areas accessible</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-005</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Random: wide spread — WO View + Schedule Edit + Timesheets View + Reports + History Logs, Financial OFF</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-006</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Random: Invoicing Delete requested with Manage AP/AR OFF — AP/AR gate fires, resolve, verify</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-007</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Random: Settings + App Settings ON (role/staff management) + WO View — verify admin subset only</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>"App Settings"=settingsApp (governs Roles/Staff mgmt per VIU). "Settings" has no distinct catalog code (settings split into settingsApp/Service/Wages/Parts/Finance/DataImport); mapped to settingsApp.; PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>CB-RND-008</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Random: arbitrary mix — Customers Delete + WO Lines Edit + Vendor View(Parts Dept ON) + Full View, Financial OFF</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Combination (Random)</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>PUT 200, assign 201, stored view_mode=full. Effective set equals stored role set (backend has no server-side cascade; UI cascade/gate pre-resolved into the PUT set, confirmed in prior VIU). fe-permissions verified as Tech via dev-login.</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t>DI-001</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>DI-002</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>DI-004</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>DI-007</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>DI-008</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>DI-009</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>DI-010</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>DI-011</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Administrator - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role has both. Verified live in Tech UI. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>DI-012</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>DI-013</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>DI-015</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>DI-018</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>DI-019</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>DI-020</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>DI-021</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>DI-022</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Service Manager - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
+        <is>
+          <t>DI-023</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>DI-024</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
+        <is>
+          <t>DI-026</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>DI-029</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="12" t="inlineStr">
+        <is>
+          <t>DI-030</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>DI-031</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>DI-032</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>DI-033</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
+        <is>
+          <t>DI-034</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>DI-035</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="12" t="inlineStr">
+        <is>
+          <t>DI-037</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>DI-040</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>DI-041</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>DI-042</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>DI-043</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
+        <is>
+          <t>DI-044</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Service Advisor - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>DI-045</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>DI-046</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>DI-048</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>DI-051</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>DI-052</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>DI-053</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>DI-054</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>DI-055</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Foreman - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>DI-056</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Technician - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>DI-057</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Technician - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>DI-059</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Technician - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>DI-062</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Technician - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>DI-063</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Technician - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>DI-064</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Technician - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
+        <is>
+          <t>DI-065</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Technician - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="12" t="inlineStr">
+        <is>
+          <t>DI-066</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Technician - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="12" t="inlineStr">
+        <is>
+          <t>DI-067</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="12" t="inlineStr">
+        <is>
+          <t>DI-068</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D185" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=Y. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="12" t="inlineStr">
+        <is>
+          <t>DI-070</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=Y (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>DI-073</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D187" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="12" t="inlineStr">
+        <is>
+          <t>DI-074</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D188" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>DI-075</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D189" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="12" t="inlineStr">
+        <is>
+          <t>DI-076</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D190" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>DI-077</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Parts Manager - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>DI-078</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>DI-079</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=N. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="12" t="inlineStr">
+        <is>
+          <t>DI-080</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>DI-081</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>DI-082</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D196" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>DI-083</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D197" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>DI-084</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D198" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>DI-085</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>DI-086</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>DI-087</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>DI-088</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Parts Technician - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D202" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role lacks settingsService so the Service menu group / Inspection Templates link is not exposed. NOTE (hardening finding): the /administration/inspection-templates route itself lacks a settingsService guard, so roles that have another settings sub-permission (e.g. Service Manager, Parts Manager) can reach a READ-ONLY view via direct URL (no "New" button); the documented Settings&gt;Service menu path is correctly denied. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>DI-089</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Office - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>DI-090</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Office - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D204" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Line-level control gating verified via authoritative effective permission workOrderLinesCreateAndEdit=N. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>DI-091</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Office - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>DI-092</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Office - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D206" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Edit-capability gated by workOrderLinesCreateAndEdit=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>DI-093</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Office - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D207" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="12" t="inlineStr">
+        <is>
+          <t>DI-094</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Office - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D208" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="12" t="inlineStr">
+        <is>
+          <t>DI-095</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Office - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D209" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="12" t="inlineStr">
+        <is>
+          <t>DI-096</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Office - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t>DI-097</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Office - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Remove control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="12" t="inlineStr">
+        <is>
+          <t>DI-098</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Office - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Reopen control gated by workOrderLinesDelete=N (verified). Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="12" t="inlineStr">
+        <is>
+          <t>DI-099</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Office - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D213" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Requires settingsApp + settingsService; role has both. Verified live in Tech UI. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="12" t="inlineStr">
+        <is>
+          <t>DI-100</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - A. View inspections on a work order line</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D214" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>DI-101</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="12" t="inlineStr">
+        <is>
+          <t>DI-102</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D216" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="12" t="inlineStr">
+        <is>
+          <t>DI-103</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D217" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="12" t="inlineStr">
+        <is>
+          <t>DI-104</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>DI-105</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D219" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="12" t="inlineStr">
+        <is>
+          <t>DI-106</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - G. Inspection status labels display correctly</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>DI-107</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D221" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="inlineStr">
+        <is>
+          <t>DI-108</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D222" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="12" t="inlineStr">
+        <is>
+          <t>DI-109</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D223" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>WO-access gate = (workOrdersView OR workOrdersCreateAndEdit) + default workplace; role has neither. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="12" t="inlineStr">
+        <is>
+          <t>DI-110</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Sales Representative - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="12" t="inlineStr">
+        <is>
+          <t>DI-112</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - B. Add inspection to a work order line</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock has WO access via workOrdersView; DI action still correctly gated off by missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="12" t="inlineStr">
+        <is>
+          <t>DI-113</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - C. Add multiple inspection templates to one line</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D226" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock DOES have WO access (workOrdersView), contradicting the precondition's "no WO access"; however the inspection action is still correctly unavailable due to missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>DI-114</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - D. Open and fill an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D227" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock has WO access via workOrdersView; DI action still correctly gated off by missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="12" t="inlineStr">
+        <is>
+          <t>DI-115</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - E. Complete an inspection (Submit and Generate Report)</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D228" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock DOES have WO access (workOrdersView), contradicting the precondition's "no WO access"; however the inspection action is still correctly unavailable due to missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>DI-116</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - F. Inspection at 100 percent but not submitted shows Open</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D229" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock DOES have WO access (workOrdersView), contradicting the precondition's "no WO access"; however the inspection action is still correctly unavailable due to missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>DI-118</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - H. Remove an in-progress inspection</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock has WO access via workOrdersView; DI action still correctly gated off by missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>DI-119</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - I. Remove a completed inspection</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D231" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock has WO access via workOrdersView; DI action still correctly gated off by missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="12" t="inlineStr">
+        <is>
+          <t>DI-120</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - J. Reopen a completed inspection</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D232" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>DRIFT NOTE: Time Clock has WO access via workOrdersView; DI action still correctly gated off by missing workOrderLines permission. Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="12" t="inlineStr">
+        <is>
+          <t>DI-121</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Time Clock - K. Configure Inspection Templates (Settings &gt; Service)</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Digital Inspections</t>
+        </is>
+      </c>
+      <c r="D233" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Basis: effective fe-permissions verified live via Tech quick-login (match=true vs intended); DI access is governed by these existing permissions (no dedicated DI/checklist permission exists in this org). Feature presence confirmed via /api/inspection-templates.</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>staging live-run 2026-07-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F233"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>